--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_atacama_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_atacama_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:17</t>
+    <t xml:space="preserve">2026-09-29 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_atacama_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_atacama_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:07</t>
+    <t xml:space="preserve">2026-09-29 18:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -504,7 +504,7 @@
         <v>-5.13</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>36.4</v>
+        <v>36.41</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>41.53</v>
@@ -518,7 +518,7 @@
         <v>-12.76</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>71.27</v>
+        <v>71.28</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>84.03</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_atacama_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_atacama_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:44</t>
+    <t xml:space="preserve">2026-10-05 04:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -507,7 +507,7 @@
         <v>36.41</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>41.53</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="4">
@@ -521,7 +521,7 @@
         <v>71.28</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>84.03</v>
+        <v>84.04</v>
       </c>
     </row>
   </sheetData>
